--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_155_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_155_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M2" t="n">
         <v>10</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M3" t="n">
         <v>12</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1534,7 +1534,7 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1923,10 +1923,10 @@
         <v>25</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2119,7 +2119,7 @@
         <v>6</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -2517,10 +2517,10 @@
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X23" t="n">
         <v>1</v>
@@ -2906,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -3298,7 +3298,7 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -3491,10 +3491,10 @@
         <v>2</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -3827,16 +3827,16 @@
         <v>114</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X30" t="n">
         <v>28</v>
@@ -4491,13 +4491,13 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X36" t="n">
         <v>2</v>
@@ -4687,13 +4687,13 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X37" t="n">
         <v>2</v>
@@ -4883,7 +4883,7 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -5272,7 +5272,7 @@
         <v>6</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
@@ -5471,13 +5471,13 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X41" t="n">
         <v>7</v>
@@ -5667,7 +5667,7 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -6056,7 +6056,7 @@
         <v>20</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
@@ -6252,16 +6252,16 @@
         <v>6</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X45" t="n">
         <v>1</v>
@@ -6784,16 +6784,16 @@
         <v>121</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="X48" t="n">
         <v>29</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_155_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_155_EL.xlsx
@@ -674,10 +674,10 @@
         <v>10</v>
       </c>
       <c r="N2" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="O2" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="P2" t="n">
         <v>7</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>87.50</t>
+          <t>75.00</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>12</v>
       </c>
       <c r="N3" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="O3" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>74.36</t>
+          <t>61.54</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
@@ -1935,14 +1935,14 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y20" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA20" t="n">
@@ -2523,14 +2523,14 @@
         <v>2</v>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA23" t="n">
@@ -2915,10 +2915,10 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="Y25" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
@@ -3307,14 +3307,14 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA27" t="n">
@@ -3503,14 +3503,14 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA28" t="n">
@@ -3839,14 +3839,14 @@
         <v>2</v>
       </c>
       <c r="X30" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="Y30" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -4892,14 +4892,14 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y38" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="AA38" t="n">
@@ -5088,14 +5088,14 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y39" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AA39" t="n">
@@ -5284,14 +5284,14 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="AA40" t="n">
@@ -5480,14 +5480,14 @@
         <v>3</v>
       </c>
       <c r="X41" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y41" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AA41" t="n">
@@ -6068,10 +6068,10 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
@@ -6796,14 +6796,14 @@
         <v>7</v>
       </c>
       <c r="X48" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="Y48" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>74.4%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="AA48" t="n">
